--- a/data/trans_dic/P36BPD01_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD01_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva</t>
+          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,52; 96,22</t>
+          <t>85,38; 96,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,79; 97,09</t>
+          <t>89,16; 96,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,04; 95,74</t>
+          <t>88,7; 95,69</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,45; 97,49</t>
+          <t>91,66; 97,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,99; 97,37</t>
+          <t>93,04; 97,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,23; 97,01</t>
+          <t>93,32; 96,82</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90,61; 95,09</t>
+          <t>90,46; 95,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,91; 95,51</t>
+          <t>91,92; 95,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,01; 94,83</t>
+          <t>92,15; 94,84</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>93,82; 98,5</t>
+          <t>93,77; 98,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,02; 96,76</t>
+          <t>93,98; 96,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,47; 97,51</t>
+          <t>94,47; 97,54</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,36; 97,56</t>
+          <t>94,19; 97,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,35; 97,04</t>
+          <t>94,33; 96,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,77; 96,84</t>
+          <t>94,77; 96,83</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95,04; 98,05</t>
+          <t>94,76; 98,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95,63; 99,05</t>
+          <t>95,59; 99,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95,91; 98,58</t>
+          <t>95,85; 98,62</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>94,45; 98,19</t>
+          <t>94,74; 98,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94,79; 97,41</t>
+          <t>94,72; 97,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95,32; 97,42</t>
+          <t>95,27; 97,45</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>94,22; 96,41</t>
+          <t>94,13; 96,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94,88; 96,43</t>
+          <t>94,85; 96,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94,8; 96,1</t>
+          <t>94,77; 96,15</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva</t>
+          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>335752; 377780</t>
+          <t>335222; 377756</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>275661; 301404</t>
+          <t>276794; 301078</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>625967; 673129</t>
+          <t>623631; 672753</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>387346; 412919</t>
+          <t>388234; 413522</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>473528; 495845</t>
+          <t>473826; 496207</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>869650; 904886</t>
+          <t>870520; 903163</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>483362; 507242</t>
+          <t>482564; 507915</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>498582; 518109</t>
+          <t>498637; 516950</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>989934; 1020313</t>
+          <t>991424; 1020352</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>829889; 871238</t>
+          <t>829418; 872767</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>669253; 688723</t>
+          <t>668955; 688646</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1508038; 1556640</t>
+          <t>1508062; 1557003</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>526691; 544563</t>
+          <t>525718; 544489</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>516339; 531070</t>
+          <t>516218; 530110</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1047576; 1070483</t>
+          <t>1047609; 1070305</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>349897; 361001</t>
+          <t>348873; 361081</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>581755; 602605</t>
+          <t>581565; 602262</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>936578; 962645</t>
+          <t>935972; 963044</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>265689; 276195</t>
+          <t>266498; 275797</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>403657; 414784</t>
+          <t>403351; 414684</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>674057; 688899</t>
+          <t>673706; 689125</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3242677; 3318017</t>
+          <t>3239663; 3314832</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3468372; 3524900</t>
+          <t>3467078; 3528030</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6728011; 6820115</t>
+          <t>6725947; 6823898</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36BPD01_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD01_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,38; 96,22</t>
+          <t>85,07; 94,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>89,16; 96,98</t>
+          <t>87,41; 95,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,7; 95,69</t>
+          <t>88,06; 94,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,66; 97,63</t>
+          <t>89,54; 95,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,04; 97,44</t>
+          <t>89,88; 95,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,32; 96,82</t>
+          <t>90,97; 94,71</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90,46; 95,22</t>
+          <t>88,26; 93,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,92; 95,3</t>
+          <t>91,92; 95,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,15; 94,84</t>
+          <t>90,73; 93,85</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>93,77; 98,67</t>
+          <t>91,66; 95,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,98; 96,75</t>
+          <t>93,32; 95,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,47; 97,54</t>
+          <t>93,08; 95,38</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,19; 97,55</t>
+          <t>93,96; 97,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,33; 96,87</t>
+          <t>94,27; 96,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,77; 96,83</t>
+          <t>94,64; 96,76</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>94,76; 98,08</t>
+          <t>94,51; 97,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95,59; 99,0</t>
+          <t>94,31; 97,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95,85; 98,62</t>
+          <t>94,83; 97,02</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>94,74; 98,05</t>
+          <t>94,67; 98,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94,72; 97,38</t>
+          <t>94,65; 97,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95,27; 97,45</t>
+          <t>94,97; 97,28</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>94,13; 96,31</t>
+          <t>92,76; 94,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94,85; 96,52</t>
+          <t>93,79; 95,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94,77; 96,15</t>
+          <t>93,5; 94,74</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>361454</t>
+          <t>364972</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>292073</t>
+          <t>331833</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>653527</t>
+          <t>696805</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>335222; 377756</t>
+          <t>341344; 381095</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>276794; 301078</t>
+          <t>314342; 344656</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>623631; 672753</t>
+          <t>669984; 718496</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>403236</t>
+          <t>444409</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>486477</t>
+          <t>462233</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>889714</t>
+          <t>906642</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>388234; 413522</t>
+          <t>427014; 457133</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>473826; 496207</t>
+          <t>447512; 473099</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>870520; 903163</t>
+          <t>886809; 923268</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>497249</t>
+          <t>563435</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>509013</t>
+          <t>583281</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1006261</t>
+          <t>1146717</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>482564; 507915</t>
+          <t>545466; 577054</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>498637; 516950</t>
+          <t>571847; 592983</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>991424; 1020352</t>
+          <t>1125259; 1163917</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>849462</t>
+          <t>654416</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>679620</t>
+          <t>697138</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1529082</t>
+          <t>1351554</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>829418; 872767</t>
+          <t>639274; 665737</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668955; 688646</t>
+          <t>686605; 705744</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1508062; 1557003</t>
+          <t>1333978; 1366958</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>536694</t>
+          <t>581016</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>524250</t>
+          <t>582166</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1060944</t>
+          <t>1163182</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>525718; 544489</t>
+          <t>569644; 589351</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>516218; 530110</t>
+          <t>573342; 589021</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1047609; 1070305</t>
+          <t>1149395; 1175044</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>356187</t>
+          <t>392070</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>592402</t>
+          <t>421189</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>948589</t>
+          <t>813259</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>348873; 361081</t>
+          <t>384730; 397588</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>581565; 602262</t>
+          <t>414194; 426210</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>935972; 963044</t>
+          <t>802485; 820987</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>272164</t>
+          <t>298298</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>409918</t>
+          <t>446340</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>682081</t>
+          <t>744638</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>266498; 275797</t>
+          <t>292066; 302769</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>403351; 414684</t>
+          <t>439741; 451754</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>673706; 689125</t>
+          <t>734189; 752051</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>3276446</t>
+          <t>3298616</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3493752</t>
+          <t>3524181</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6770198</t>
+          <t>6822797</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3239663; 3314832</t>
+          <t>3260980; 3328952</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3467078; 3528030</t>
+          <t>3495998; 3551130</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6725947; 6823898</t>
+          <t>6771769; 6861831</t>
         </is>
       </c>
     </row>
